--- a/timesheet-template.xlsx
+++ b/timesheet-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timesheet" sheetId="1" r:id="R3f9ff08da8584cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timesheet" sheetId="1" r:id="Red9c7fb766ed468a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Amended">Timesheet!$AI$4</x:definedName>
@@ -978,9 +978,6 @@
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">David Ingleston</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Payroll Number</x:t>
   </x:si>
   <x:si>
@@ -1334,9 +1331,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Employee Sign</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D Ingleston</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">I declare that the hours booked are properly claimed, accurate &amp; complete</x:t>
@@ -4708,13 +4702,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="/xl/media/image1.png"/>
+        <xdr:cNvPr id="22" name="/xl/media/image.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R932a13cf42e34d42"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7fba22eaf84b42cd"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5229,9 +5223,7 @@
       <x:c r="BA4" s="53">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BB4" s="54">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="BB4" s="54"/>
       <x:c r="BC4" s="29"/>
       <x:c r="BD4" s="29"/>
       <x:c r="BE4" s="29"/>
@@ -5239,16 +5231,16 @@
       <x:c r="BP4" s="48" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="BQ4" s="49" t="str">
+      <x:c r="BQ4" s="49" t="e">
         <x:f>IF(SUM($BS$4:$BS$5)=BR4,"OK","Check")</x:f>
-        <x:v>Check</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BR4" s="50">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS4" s="50">
+      <x:c r="BS4" s="50" t="e">
         <x:f>IF(Current&lt;&gt;"",1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BT4" s="17"/>
       <x:c r="BU4" s="17"/>
@@ -5307,16 +5299,16 @@
       <x:c r="BP5" s="48" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="BQ5" s="49" t="str">
+      <x:c r="BQ5" s="49" t="e">
         <x:f>IF(SUM($BS$4:$BS$5)=BR5,"OK","Check")</x:f>
-        <x:v>Check</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BR5" s="50">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS5" s="50">
+      <x:c r="BS5" s="50" t="e">
         <x:f>IF(Amended&lt;&gt;"",1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BT5" s="17"/>
       <x:c r="BU5" s="17"/>
@@ -5354,9 +5346,7 @@
       <x:c r="D6" s="131"/>
       <x:c r="E6" s="131"/>
       <x:c r="F6" s="131"/>
-      <x:c r="G6" s="270" t="s">
-        <x:v>25</x:v>
-      </x:c>
+      <x:c r="G6" s="270"/>
       <x:c r="H6" s="271"/>
       <x:c r="I6" s="271"/>
       <x:c r="J6" s="271"/>
@@ -5373,58 +5363,34 @@
       <x:c r="U6" s="272"/>
       <x:c r="V6" s="4"/>
       <x:c r="W6" s="131" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="X6" s="131"/>
       <x:c r="Y6" s="131"/>
       <x:c r="Z6" s="131"/>
-      <x:c r="AA6" s="59">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB6" s="82">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="AC6" s="83">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="AD6" s="82">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="AE6" s="82">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="AF6" s="82">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="AA6" s="59"/>
+      <x:c r="AB6" s="82"/>
+      <x:c r="AC6" s="83"/>
+      <x:c r="AD6" s="82"/>
+      <x:c r="AE6" s="82"/>
+      <x:c r="AF6" s="82"/>
       <x:c r="AG6" s="131" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AH6" s="131"/>
       <x:c r="AI6" s="131"/>
       <x:c r="AJ6" s="131"/>
       <x:c r="AK6" s="131"/>
-      <x:c r="AL6" s="59">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="AL6" s="59"/>
       <x:c r="AM6" s="59"/>
-      <x:c r="AN6" s="59">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="AO6" s="59">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP6" s="59">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AQ6" s="59">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR6" s="59">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="AN6" s="59"/>
+      <x:c r="AO6" s="59"/>
+      <x:c r="AP6" s="59"/>
+      <x:c r="AQ6" s="59"/>
+      <x:c r="AR6" s="59"/>
       <x:c r="AS6" s="4"/>
       <x:c r="AT6" s="239" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AU6" s="240"/>
       <x:c r="AV6" s="240"/>
@@ -5432,24 +5398,12 @@
       <x:c r="AX6" s="240"/>
       <x:c r="AY6" s="240"/>
       <x:c r="AZ6" s="241"/>
-      <x:c r="BA6" s="53">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BB6" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC6" s="53">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD6" s="54">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="BE6" s="53">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BF6" s="54">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="BA6" s="53"/>
+      <x:c r="BB6" s="54"/>
+      <x:c r="BC6" s="53"/>
+      <x:c r="BD6" s="54"/>
+      <x:c r="BE6" s="53"/>
+      <x:c r="BF6" s="54"/>
       <x:c r="BH6" s="5"/>
       <x:c r="BI6" s="5"/>
       <x:c r="BJ6" s="5"/>
@@ -5457,18 +5411,18 @@
       <x:c r="BL6" s="5"/>
       <x:c r="BM6" s="22"/>
       <x:c r="BP6" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BQ6" s="49" t="str">
         <x:f t="shared" ref="BQ6:BQ11" si="0">IF(BS6=BR6,"OK","Check")</x:f>
-        <x:v>OK</x:v>
+        <x:v>Check</x:v>
       </x:c>
       <x:c r="BR6" s="50">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="BS6" s="50">
+      <x:c r="BS6" s="50" t="n">
         <x:f>COUNT(Week_Number)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BT6" s="17"/>
       <x:c r="BU6" s="17"/>
@@ -5493,13 +5447,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="CG6" s="51" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18.75" customHeight="1">
       <x:c r="B7" s="23"/>
       <x:c r="W7" s="115" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="X7" s="115"/>
       <x:c r="Y7" s="115"/>
@@ -5511,7 +5465,7 @@
       <x:c r="AE7" s="115"/>
       <x:c r="BM7" s="22"/>
       <x:c r="BP7" s="48" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BQ7" s="49" t="str">
         <x:f t="shared" si="0"/>
@@ -5520,9 +5474,9 @@
       <x:c r="BR7" s="50">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="BS7" s="50">
+      <x:c r="BS7" s="50" t="n">
         <x:f>COUNTA(Payroll_Number)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BT7" s="17"/>
       <x:c r="BU7" s="17"/>
@@ -5545,14 +5499,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CG7" s="51" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30.75" customHeight="1">
       <x:c r="B8" s="23"/>
       <x:c r="C8" s="8"/>
       <x:c r="AP8" s="225" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="AQ8" s="226"/>
       <x:c r="AR8" s="226"/>
@@ -5564,7 +5518,7 @@
       <x:c r="AX8" s="227"/>
       <x:c r="BM8" s="22"/>
       <x:c r="BP8" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="BQ8" s="49" t="str">
         <x:f t="shared" si="0"/>
@@ -5573,9 +5527,9 @@
       <x:c r="BR8" s="50">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="BS8" s="50">
+      <x:c r="BS8" s="50" t="n">
         <x:f>COUNT(Cost_Centre)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BT8" s="17"/>
       <x:c r="BU8" s="17"/>
@@ -5596,7 +5550,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="CG8" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="23.25" customHeight="1">
@@ -5612,7 +5566,7 @@
       <x:c r="AX9" s="230"/>
       <x:c r="BM9" s="22"/>
       <x:c r="BP9" s="48" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BQ9" s="49" t="str">
         <x:f t="shared" si="0"/>
@@ -5621,9 +5575,9 @@
       <x:c r="BR9" s="50">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="BS9" s="50">
+      <x:c r="BS9" s="50" t="n">
         <x:f>COUNT(Week_Ending)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BT9" s="17"/>
       <x:c r="BU9" s="17"/>
@@ -5644,13 +5598,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="CG9" s="51" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="B10" s="23"/>
       <x:c r="C10" s="279" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="280"/>
       <x:c r="E10" s="280"/>
@@ -5659,88 +5613,88 @@
       <x:c r="H10" s="281"/>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="285" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K10" s="287"/>
       <x:c r="L10" s="260" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M10" s="261"/>
       <x:c r="N10" s="261"/>
       <x:c r="O10" s="262"/>
       <x:c r="P10" s="219" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q10" s="221"/>
       <x:c r="R10" s="273" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="S10" s="220"/>
       <x:c r="T10" s="220"/>
       <x:c r="U10" s="221"/>
       <x:c r="V10" s="273" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="W10" s="220"/>
       <x:c r="X10" s="220"/>
       <x:c r="Y10" s="221"/>
       <x:c r="Z10" s="273" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AA10" s="220"/>
       <x:c r="AB10" s="220"/>
       <x:c r="AC10" s="221"/>
       <x:c r="AD10" s="285" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE10" s="286"/>
       <x:c r="AF10" s="286"/>
       <x:c r="AG10" s="287"/>
       <x:c r="AH10" s="62" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AI10" s="219" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="AI10" s="219" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="AJ10" s="220"/>
       <x:c r="AK10" s="220"/>
       <x:c r="AL10" s="221"/>
       <x:c r="AM10" s="63" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AN10" s="219" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="AN10" s="219" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="AO10" s="221"/>
       <x:c r="AP10" s="219" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ10" s="220"/>
       <x:c r="AR10" s="221"/>
       <x:c r="AS10" s="231" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT10" s="233"/>
       <x:c r="AU10" s="231" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AV10" s="233"/>
       <x:c r="AW10" s="231" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AX10" s="233"/>
       <x:c r="AY10" s="219" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AZ10" s="221"/>
       <x:c r="BA10" s="231" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB10" s="232"/>
       <x:c r="BC10" s="232"/>
       <x:c r="BD10" s="233"/>
       <x:c r="BE10" s="219" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF10" s="220"/>
       <x:c r="BG10" s="220"/>
@@ -5751,7 +5705,7 @@
       <x:c r="BL10" s="221"/>
       <x:c r="BM10" s="22"/>
       <x:c r="BP10" s="48" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BQ10" s="49" t="str">
         <x:f t="shared" si="0"/>
@@ -5760,9 +5714,9 @@
       <x:c r="BR10" s="50">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS10" s="50">
+      <x:c r="BS10" s="50" t="e">
         <x:f>IF(Employee_Sign&lt;&gt;"",1,0)</x:f>
-        <x:v>1</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BT10" s="17"/>
       <x:c r="BU10" s="17"/>
@@ -5781,7 +5735,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="CG10" s="51" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28.5" customHeight="1">
@@ -5796,7 +5750,7 @@
       <x:c r="J11" s="288"/>
       <x:c r="K11" s="264"/>
       <x:c r="L11" s="267" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M11" s="268"/>
       <x:c r="N11" s="268"/>
@@ -5804,32 +5758,32 @@
       <x:c r="P11" s="263"/>
       <x:c r="Q11" s="264"/>
       <x:c r="R11" s="267" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S11" s="268"/>
       <x:c r="T11" s="268"/>
       <x:c r="U11" s="269"/>
       <x:c r="V11" s="267" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W11" s="268"/>
       <x:c r="X11" s="268"/>
       <x:c r="Y11" s="269"/>
       <x:c r="Z11" s="267" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AA11" s="268"/>
       <x:c r="AB11" s="268"/>
       <x:c r="AC11" s="269"/>
       <x:c r="AD11" s="267" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AE11" s="268"/>
       <x:c r="AF11" s="268"/>
       <x:c r="AG11" s="269"/>
       <x:c r="AH11" s="61"/>
       <x:c r="AI11" s="236" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AJ11" s="237"/>
       <x:c r="AK11" s="237"/>
@@ -5841,7 +5795,7 @@
       <x:c r="AQ11" s="223"/>
       <x:c r="AR11" s="224"/>
       <x:c r="AS11" s="234" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT11" s="242"/>
       <x:c r="AU11" s="242"/>
@@ -5851,11 +5805,11 @@
       <x:c r="AY11" s="222"/>
       <x:c r="AZ11" s="224"/>
       <x:c r="BA11" s="234" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB11" s="235"/>
       <x:c r="BC11" s="234" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BD11" s="235"/>
       <x:c r="BE11" s="222"/>
@@ -5868,7 +5822,7 @@
       <x:c r="BL11" s="224"/>
       <x:c r="BM11" s="22"/>
       <x:c r="BP11" s="48" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BQ11" s="49" t="str">
         <x:f t="shared" si="0"/>
@@ -5877,9 +5831,9 @@
       <x:c r="BR11" s="50">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BS11" s="50">
+      <x:c r="BS11" s="50" t="e">
         <x:f>IF(Manager_Sign&lt;&gt;"",1,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="BT11" s="17"/>
       <x:c r="BU11" s="17"/>
@@ -5898,16 +5852,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="CG11" s="51" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="36.75" customHeight="1">
       <x:c r="B12" s="23"/>
       <x:c r="C12" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D12" s="265" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D12" s="265" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="E12" s="265"/>
       <x:c r="F12" s="265"/>
@@ -5915,7 +5869,7 @@
       <x:c r="H12" s="266"/>
       <x:c r="I12" s="17"/>
       <x:c r="J12" s="254" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K12" s="257">
         <x:v>1</x:v>
@@ -5977,18 +5931,18 @@
       <x:c r="BL12" s="201"/>
       <x:c r="BM12" s="22"/>
       <x:c r="BP12" s="48" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BQ12" s="49" t="str">
         <x:f>IF(BS12&gt;0,"OK","Check")</x:f>
-        <x:v>OK</x:v>
+        <x:v>Check</x:v>
       </x:c>
       <x:c r="BR12" s="50">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="BS12" s="50">
+      <x:c r="BS12" s="50" t="n">
         <x:f>COUNTA(Surname)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BT12" s="17"/>
       <x:c r="BU12" s="17"/>
@@ -6007,16 +5961,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="CG12" s="51" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36.75" customHeight="1">
       <x:c r="B13" s="23"/>
       <x:c r="C13" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D13" s="90" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="D13" s="90" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="E13" s="90"/>
       <x:c r="F13" s="90"/>
@@ -6025,23 +5979,17 @@
       <x:c r="I13" s="17"/>
       <x:c r="J13" s="255"/>
       <x:c r="K13" s="255"/>
-      <x:c r="L13" s="95">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="L13" s="95"/>
       <x:c r="M13" s="96"/>
       <x:c r="N13" s="96"/>
       <x:c r="O13" s="97"/>
       <x:c r="P13" s="197"/>
       <x:c r="Q13" s="198"/>
-      <x:c r="R13" s="95">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="R13" s="95"/>
       <x:c r="S13" s="96"/>
       <x:c r="T13" s="96"/>
       <x:c r="U13" s="97"/>
-      <x:c r="V13" s="95">
-        <x:v>0.25</x:v>
-      </x:c>
+      <x:c r="V13" s="95"/>
       <x:c r="W13" s="96"/>
       <x:c r="X13" s="96"/>
       <x:c r="Y13" s="97"/>
@@ -6054,9 +6002,7 @@
       <x:c r="AF13" s="96"/>
       <x:c r="AG13" s="97"/>
       <x:c r="AH13" s="69"/>
-      <x:c r="AI13" s="119">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="AI13" s="119"/>
       <x:c r="AJ13" s="120"/>
       <x:c r="AK13" s="120"/>
       <x:c r="AL13" s="121"/>
@@ -6108,16 +6054,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="CG13" s="51" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36.75" customHeight="1">
       <x:c r="B14" s="23"/>
       <x:c r="C14" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D14" s="90" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="D14" s="90" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="90"/>
       <x:c r="F14" s="90"/>
@@ -6199,16 +6145,16 @@
       <x:c r="CE14" s="17"/>
       <x:c r="CF14" s="17"/>
       <x:c r="CG14" s="51" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36.75" customHeight="1">
       <x:c r="B15" s="23"/>
       <x:c r="C15" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D15" s="90" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="D15" s="90" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="E15" s="90"/>
       <x:c r="F15" s="90"/>
@@ -6216,7 +6162,7 @@
       <x:c r="H15" s="91"/>
       <x:c r="I15" s="17"/>
       <x:c r="J15" s="254" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K15" s="257">
         <x:v>2</x:v>
@@ -6278,23 +6224,23 @@
       <x:c r="BL15" s="201"/>
       <x:c r="BM15" s="22"/>
       <x:c r="BP15" s="307" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BQ15" s="308"/>
       <x:c r="BR15" s="306" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BS15" s="306"/>
       <x:c r="BT15" s="306"/>
       <x:c r="BU15" s="306"/>
       <x:c r="BV15" s="44" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BW15" s="44" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="BW15" s="44" t="s">
+      <x:c r="BX15" s="44" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="BX15" s="44" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="BZ15" s="17"/>
       <x:c r="CA15" s="17"/>
@@ -6304,16 +6250,16 @@
       <x:c r="CE15" s="17"/>
       <x:c r="CF15" s="17"/>
       <x:c r="CG15" s="51" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36.75" customHeight="1">
       <x:c r="B16" s="23"/>
       <x:c r="C16" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D16" s="90" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="D16" s="90" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="E16" s="90"/>
       <x:c r="F16" s="90"/>
@@ -6322,23 +6268,17 @@
       <x:c r="I16" s="17"/>
       <x:c r="J16" s="255"/>
       <x:c r="K16" s="255"/>
-      <x:c r="L16" s="95">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="L16" s="95"/>
       <x:c r="M16" s="96"/>
       <x:c r="N16" s="96"/>
       <x:c r="O16" s="97"/>
       <x:c r="P16" s="197"/>
       <x:c r="Q16" s="198"/>
-      <x:c r="R16" s="95">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="R16" s="95"/>
       <x:c r="S16" s="96"/>
       <x:c r="T16" s="96"/>
       <x:c r="U16" s="97"/>
-      <x:c r="V16" s="95">
-        <x:v>0.25</x:v>
-      </x:c>
+      <x:c r="V16" s="95"/>
       <x:c r="W16" s="96"/>
       <x:c r="X16" s="96"/>
       <x:c r="Y16" s="97"/>
@@ -6351,9 +6291,7 @@
       <x:c r="AF16" s="96"/>
       <x:c r="AG16" s="97"/>
       <x:c r="AH16" s="69"/>
-      <x:c r="AI16" s="128">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="AI16" s="128"/>
       <x:c r="AJ16" s="129"/>
       <x:c r="AK16" s="129"/>
       <x:c r="AL16" s="130"/>
@@ -6389,19 +6327,19 @@
       <x:c r="BP16" s="309"/>
       <x:c r="BQ16" s="310"/>
       <x:c r="BR16" s="49" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BS16" s="49" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BT16" s="49" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="BU16" s="49" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="BV16" s="304" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="BU16" s="49" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="BV16" s="304" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="BW16" s="304"/>
       <x:c r="BX16" s="304"/>
@@ -6413,16 +6351,16 @@
       <x:c r="CE16" s="17"/>
       <x:c r="CF16" s="17"/>
       <x:c r="CG16" s="51" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="36.75" customHeight="1">
       <x:c r="B17" s="23"/>
       <x:c r="C17" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D17" s="90" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="D17" s="90" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="E17" s="90"/>
       <x:c r="F17" s="90"/>
@@ -6488,7 +6426,7 @@
       <x:c r="BL17" s="218"/>
       <x:c r="BM17" s="22"/>
       <x:c r="BP17" s="274" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BQ17" s="274">
         <x:v>1</x:v>
@@ -6529,16 +6467,16 @@
       <x:c r="CE17" s="17"/>
       <x:c r="CF17" s="17"/>
       <x:c r="CG17" s="51" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="36.75" customHeight="1">
       <x:c r="B18" s="23"/>
       <x:c r="C18" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D18" s="90" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="D18" s="90" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="E18" s="90"/>
       <x:c r="F18" s="90"/>
@@ -6546,7 +6484,7 @@
       <x:c r="H18" s="91"/>
       <x:c r="I18" s="17"/>
       <x:c r="J18" s="254" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K18" s="257">
         <x:v>3</x:v>
@@ -6607,9 +6545,9 @@
       <x:c r="BM18" s="22"/>
       <x:c r="BP18" s="275"/>
       <x:c r="BQ18" s="275"/>
-      <x:c r="BR18" s="50">
+      <x:c r="BR18" s="50" t="str">
         <x:f>IF(Timesheet!L13="","No Data",Timesheet!L13)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>No Data</x:v>
       </x:c>
       <x:c r="BS18" s="50" t="str">
         <x:f>IF(Timesheet!M13="","No Data",Timesheet!M13)</x:f>
@@ -6625,15 +6563,15 @@
       </x:c>
       <x:c r="BV18" s="50" t="str">
         <x:f>IF(BR18="No Data","OK",IF(Timesheet!AS13="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BW18" s="50" t="str">
         <x:f>IF(BR18="No Data","OK",IF(Timesheet!AU13="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BX18" s="50" t="str">
         <x:f>IF(BR18="No Data","OK",IF(Timesheet!AW13="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BZ18" s="17"/>
       <x:c r="CA18" s="17"/>
@@ -6643,16 +6581,16 @@
       <x:c r="CE18" s="17"/>
       <x:c r="CF18" s="17"/>
       <x:c r="CG18" s="51" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36.75" customHeight="1">
       <x:c r="B19" s="23"/>
       <x:c r="C19" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D19" s="90" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="D19" s="90" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="E19" s="90"/>
       <x:c r="F19" s="90"/>
@@ -6661,23 +6599,17 @@
       <x:c r="I19" s="17"/>
       <x:c r="J19" s="255"/>
       <x:c r="K19" s="255"/>
-      <x:c r="L19" s="95">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="L19" s="95"/>
       <x:c r="M19" s="96"/>
       <x:c r="N19" s="96"/>
       <x:c r="O19" s="97"/>
       <x:c r="P19" s="197"/>
       <x:c r="Q19" s="198"/>
-      <x:c r="R19" s="95">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="R19" s="95"/>
       <x:c r="S19" s="96"/>
       <x:c r="T19" s="96"/>
       <x:c r="U19" s="97"/>
-      <x:c r="V19" s="95">
-        <x:v>0.25</x:v>
-      </x:c>
+      <x:c r="V19" s="95"/>
       <x:c r="W19" s="96"/>
       <x:c r="X19" s="96"/>
       <x:c r="Y19" s="97"/>
@@ -6690,9 +6622,7 @@
       <x:c r="AF19" s="96"/>
       <x:c r="AG19" s="97"/>
       <x:c r="AH19" s="69"/>
-      <x:c r="AI19" s="168">
-        <x:v>4.1666666666666664E-2</x:v>
-      </x:c>
+      <x:c r="AI19" s="168"/>
       <x:c r="AJ19" s="169"/>
       <x:c r="AK19" s="169"/>
       <x:c r="AL19" s="170"/>
@@ -6761,16 +6691,16 @@
       <x:c r="CE19" s="17"/>
       <x:c r="CF19" s="17"/>
       <x:c r="CG19" s="51" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="36.75" customHeight="1">
       <x:c r="B20" s="23"/>
       <x:c r="C20" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D20" s="90" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="D20" s="90" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="E20" s="90"/>
       <x:c r="F20" s="90"/>
@@ -6836,7 +6766,7 @@
       <x:c r="BL20" s="218"/>
       <x:c r="BM20" s="22"/>
       <x:c r="BP20" s="274" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BQ20" s="274">
         <x:v>2</x:v>
@@ -6877,16 +6807,16 @@
       <x:c r="CE20" s="17"/>
       <x:c r="CF20" s="17"/>
       <x:c r="CG20" s="51" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="36.75" customHeight="1">
       <x:c r="B21" s="23"/>
       <x:c r="C21" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D21" s="90" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="D21" s="90" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="E21" s="90"/>
       <x:c r="F21" s="90"/>
@@ -6894,7 +6824,7 @@
       <x:c r="H21" s="91"/>
       <x:c r="I21" s="17"/>
       <x:c r="J21" s="254" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K21" s="257">
         <x:v>4</x:v>
@@ -6957,9 +6887,9 @@
       <x:c r="BM21" s="22"/>
       <x:c r="BP21" s="275"/>
       <x:c r="BQ21" s="275"/>
-      <x:c r="BR21" s="50">
+      <x:c r="BR21" s="50" t="str">
         <x:f>IF(Timesheet!L16="","No Data",Timesheet!L16)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>No Data</x:v>
       </x:c>
       <x:c r="BS21" s="50" t="str">
         <x:f>IF(Timesheet!M16="","No Data",Timesheet!M16)</x:f>
@@ -6975,15 +6905,15 @@
       </x:c>
       <x:c r="BV21" s="50" t="str">
         <x:f>IF(BR21="No Data","OK",IF(Timesheet!AS16="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BW21" s="50" t="str">
         <x:f>IF(BR21="No Data","OK",IF(Timesheet!AU16="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BX21" s="50" t="str">
         <x:f>IF(BR21="No Data","OK",IF(Timesheet!AW16="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BZ21" s="17"/>
       <x:c r="CA21" s="17"/>
@@ -6993,16 +6923,16 @@
       <x:c r="CE21" s="17"/>
       <x:c r="CF21" s="17"/>
       <x:c r="CG21" s="51" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="36.75" customHeight="1">
       <x:c r="B22" s="23"/>
       <x:c r="C22" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D22" s="90" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="D22" s="90" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="E22" s="90"/>
       <x:c r="F22" s="90"/>
@@ -7011,23 +6941,17 @@
       <x:c r="I22" s="17"/>
       <x:c r="J22" s="255"/>
       <x:c r="K22" s="255"/>
-      <x:c r="L22" s="95">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="L22" s="95"/>
       <x:c r="M22" s="96"/>
       <x:c r="N22" s="96"/>
       <x:c r="O22" s="97"/>
       <x:c r="P22" s="197"/>
       <x:c r="Q22" s="198"/>
-      <x:c r="R22" s="95">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="R22" s="95"/>
       <x:c r="S22" s="96"/>
       <x:c r="T22" s="96"/>
       <x:c r="U22" s="97"/>
-      <x:c r="V22" s="95">
-        <x:v>0.25</x:v>
-      </x:c>
+      <x:c r="V22" s="95"/>
       <x:c r="W22" s="96"/>
       <x:c r="X22" s="96"/>
       <x:c r="Y22" s="97"/>
@@ -7040,9 +6964,7 @@
       <x:c r="AF22" s="96"/>
       <x:c r="AG22" s="97"/>
       <x:c r="AH22" s="69"/>
-      <x:c r="AI22" s="174">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="AI22" s="174"/>
       <x:c r="AJ22" s="175"/>
       <x:c r="AK22" s="175"/>
       <x:c r="AL22" s="176"/>
@@ -7113,16 +7035,16 @@
       <x:c r="CE22" s="17"/>
       <x:c r="CF22" s="17"/>
       <x:c r="CG22" s="51" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="36.75" customHeight="1">
       <x:c r="B23" s="23"/>
       <x:c r="C23" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D23" s="90" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="D23" s="90" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="E23" s="90"/>
       <x:c r="F23" s="90"/>
@@ -7188,7 +7110,7 @@
       <x:c r="BL23" s="218"/>
       <x:c r="BM23" s="22"/>
       <x:c r="BP23" s="274" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BQ23" s="274">
         <x:v>3</x:v>
@@ -7229,16 +7151,16 @@
       <x:c r="CE23" s="17"/>
       <x:c r="CF23" s="17"/>
       <x:c r="CG23" s="51" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36.75" customHeight="1">
       <x:c r="B24" s="23"/>
       <x:c r="C24" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D24" s="90" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="D24" s="90" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="E24" s="90"/>
       <x:c r="F24" s="90"/>
@@ -7246,7 +7168,7 @@
       <x:c r="H24" s="91"/>
       <x:c r="I24" s="17"/>
       <x:c r="J24" s="254" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K24" s="257">
         <x:v>5</x:v>
@@ -7309,9 +7231,9 @@
       <x:c r="BM24" s="22"/>
       <x:c r="BP24" s="275"/>
       <x:c r="BQ24" s="275"/>
-      <x:c r="BR24" s="50">
+      <x:c r="BR24" s="50" t="str">
         <x:f>IF(Timesheet!L19="","No Data",Timesheet!L19)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>No Data</x:v>
       </x:c>
       <x:c r="BS24" s="50" t="str">
         <x:f>IF(Timesheet!M19="","No Data",Timesheet!M19)</x:f>
@@ -7327,15 +7249,15 @@
       </x:c>
       <x:c r="BV24" s="50" t="str">
         <x:f>IF(BR24="No Data","OK",IF(Timesheet!AS19="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BW24" s="50" t="str">
         <x:f>IF(BR24="No Data","OK",IF(Timesheet!AU19="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BX24" s="50" t="str">
         <x:f>IF(BR24="No Data","OK",IF(Timesheet!AW19="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BZ24" s="17"/>
       <x:c r="CA24" s="17"/>
@@ -7345,16 +7267,16 @@
       <x:c r="CE24" s="17"/>
       <x:c r="CF24" s="17"/>
       <x:c r="CG24" s="51" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="36.75" customHeight="1">
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D25" s="90" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="D25" s="90" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="E25" s="90"/>
       <x:c r="F25" s="90"/>
@@ -7367,9 +7289,7 @@
       <x:c r="M25" s="96"/>
       <x:c r="N25" s="96"/>
       <x:c r="O25" s="97"/>
-      <x:c r="P25" s="197" t="s">
-        <x:v>113</x:v>
-      </x:c>
+      <x:c r="P25" s="197"/>
       <x:c r="Q25" s="198"/>
       <x:c r="R25" s="95"/>
       <x:c r="S25" s="96"/>
@@ -7459,16 +7379,16 @@
       <x:c r="CE25" s="17"/>
       <x:c r="CF25" s="17"/>
       <x:c r="CG25" s="51" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="36.75" customHeight="1">
       <x:c r="B26" s="23"/>
       <x:c r="C26" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D26" s="90" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="D26" s="90" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="E26" s="90"/>
       <x:c r="F26" s="90"/>
@@ -7534,7 +7454,7 @@
       <x:c r="BL26" s="218"/>
       <x:c r="BM26" s="22"/>
       <x:c r="BP26" s="274" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BQ26" s="274">
         <x:v>4</x:v>
@@ -7575,16 +7495,16 @@
       <x:c r="CE26" s="17"/>
       <x:c r="CF26" s="17"/>
       <x:c r="CG26" s="51" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="36.75" customHeight="1">
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D27" s="90" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="D27" s="90" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="E27" s="90"/>
       <x:c r="F27" s="90"/>
@@ -7592,7 +7512,7 @@
       <x:c r="H27" s="91"/>
       <x:c r="I27" s="17"/>
       <x:c r="J27" s="254" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K27" s="257">
         <x:v>6</x:v>
@@ -7655,9 +7575,9 @@
       <x:c r="BM27" s="22"/>
       <x:c r="BP27" s="275"/>
       <x:c r="BQ27" s="275"/>
-      <x:c r="BR27" s="50">
+      <x:c r="BR27" s="50" t="str">
         <x:f>IF(Timesheet!L22="","No Data",Timesheet!L22)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>No Data</x:v>
       </x:c>
       <x:c r="BS27" s="50" t="str">
         <x:f>IF(Timesheet!M22="","No Data",Timesheet!M22)</x:f>
@@ -7673,15 +7593,15 @@
       </x:c>
       <x:c r="BV27" s="50" t="str">
         <x:f>IF(BR27="No Data","OK",IF(Timesheet!AS22="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BW27" s="50" t="str">
         <x:f>IF(BR27="No Data","OK",IF(Timesheet!AU22="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BX27" s="50" t="str">
         <x:f>IF(BR27="No Data","OK",IF(Timesheet!AW22="","Check","OK"))</x:f>
-        <x:v>Check</x:v>
+        <x:v>OK</x:v>
       </x:c>
       <x:c r="BZ27" s="17"/>
       <x:c r="CA27" s="17"/>
@@ -7697,10 +7617,10 @@
     <x:row r="28" ht="36.75" customHeight="1">
       <x:c r="B28" s="23"/>
       <x:c r="C28" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D28" s="90" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="D28" s="90" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="E28" s="90"/>
       <x:c r="F28" s="90"/>
@@ -7713,9 +7633,7 @@
       <x:c r="M28" s="96"/>
       <x:c r="N28" s="96"/>
       <x:c r="O28" s="97"/>
-      <x:c r="P28" s="197" t="s">
-        <x:v>113</x:v>
-      </x:c>
+      <x:c r="P28" s="197"/>
       <x:c r="Q28" s="198"/>
       <x:c r="R28" s="95"/>
       <x:c r="S28" s="96"/>
@@ -7805,16 +7723,16 @@
       <x:c r="CE28" s="17"/>
       <x:c r="CF28" s="17"/>
       <x:c r="CG28" s="51" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="36.75" customHeight="1">
       <x:c r="B29" s="23"/>
       <x:c r="C29" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D29" s="90" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="D29" s="90" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="E29" s="90"/>
       <x:c r="F29" s="90"/>
@@ -7880,7 +7798,7 @@
       <x:c r="BL29" s="218"/>
       <x:c r="BM29" s="22"/>
       <x:c r="BP29" s="274" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BQ29" s="274">
         <x:v>5</x:v>
@@ -7921,16 +7839,16 @@
       <x:c r="CE29" s="17"/>
       <x:c r="CF29" s="17"/>
       <x:c r="CG29" s="51" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="36.75" customHeight="1">
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D30" s="265" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="D30" s="265" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="E30" s="265"/>
       <x:c r="F30" s="265"/>
@@ -7938,7 +7856,7 @@
       <x:c r="H30" s="266"/>
       <x:c r="I30" s="17"/>
       <x:c r="J30" s="254" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K30" s="257">
         <x:v>7</x:v>
@@ -8033,10 +7951,10 @@
     <x:row r="31" ht="36.75" customHeight="1">
       <x:c r="B31" s="23"/>
       <x:c r="C31" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D31" s="90" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="D31" s="90" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="E31" s="90"/>
       <x:c r="F31" s="90"/>
@@ -8049,9 +7967,7 @@
       <x:c r="M31" s="96"/>
       <x:c r="N31" s="96"/>
       <x:c r="O31" s="97"/>
-      <x:c r="P31" s="197" t="s">
-        <x:v>113</x:v>
-      </x:c>
+      <x:c r="P31" s="197"/>
       <x:c r="Q31" s="198"/>
       <x:c r="R31" s="95"/>
       <x:c r="S31" s="96"/>
@@ -8137,10 +8053,10 @@
     <x:row r="32" ht="36.75" customHeight="1">
       <x:c r="B32" s="23"/>
       <x:c r="C32" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D32" s="90" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="D32" s="90" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="E32" s="90"/>
       <x:c r="F32" s="90"/>
@@ -8206,7 +8122,7 @@
       <x:c r="BL32" s="218"/>
       <x:c r="BM32" s="22"/>
       <x:c r="BP32" s="274" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BQ32" s="274">
         <x:v>6</x:v>
@@ -8244,10 +8160,10 @@
       <x:c r="A33" s="6"/>
       <x:c r="B33" s="24"/>
       <x:c r="C33" s="16" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D33" s="277" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="D33" s="277" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="E33" s="277"/>
       <x:c r="F33" s="277"/>
@@ -8255,12 +8171,11 @@
       <x:c r="H33" s="278"/>
       <x:c r="I33" s="18"/>
       <x:c r="J33" s="88" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K33" s="89"/>
-      <x:c r="L33" s="85">
+      <x:c r="L33" s="85" t="str">
         <x:f>IF(SUM(L12:L32)=0,"",SUM(L12:L32))</x:f>
-        <x:v>2</x:v>
       </x:c>
       <x:c r="M33" s="86"/>
       <x:c r="N33" s="86"/>
@@ -8280,18 +8195,17 @@
       <x:c r="AB33" s="18"/>
       <x:c r="AC33" s="18"/>
       <x:c r="AD33" s="248" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="AE33" s="249"/>
       <x:c r="AF33" s="249"/>
       <x:c r="AG33" s="250"/>
-      <x:c r="AH33" s="66">
+      <x:c r="AH33" s="66" t="n">
         <x:f>SUM(AH12:AH32)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI33" s="134">
+      <x:c r="AI33" s="134" t="str">
         <x:f>IF(SUM(AI12:AL32)=0,"",SUM(AI12:AL32))</x:f>
-        <x:v>0.54166666666666663</x:v>
       </x:c>
       <x:c r="AJ33" s="135"/>
       <x:c r="AK33" s="135"/>
@@ -8306,7 +8220,7 @@
       <x:c r="AQ33" s="18"/>
       <x:c r="AR33" s="18"/>
       <x:c r="AS33" s="295" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AT33" s="296"/>
       <x:c r="AU33" s="296"/>
@@ -8486,14 +8400,12 @@
       <x:c r="A35" s="6"/>
       <x:c r="B35" s="24"/>
       <x:c r="C35" s="189" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D35" s="190"/>
       <x:c r="E35" s="190"/>
       <x:c r="F35" s="191"/>
-      <x:c r="G35" s="298" t="s">
-        <x:v>141</x:v>
-      </x:c>
+      <x:c r="G35" s="298"/>
       <x:c r="H35" s="299"/>
       <x:c r="I35" s="299"/>
       <x:c r="J35" s="299"/>
@@ -8502,7 +8414,7 @@
       <x:c r="M35" s="299"/>
       <x:c r="N35" s="300"/>
       <x:c r="O35" s="177" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="P35" s="178"/>
       <x:c r="Q35" s="178"/>
@@ -8511,7 +8423,7 @@
       <x:c r="T35" s="179"/>
       <x:c r="U35" s="18"/>
       <x:c r="V35" s="189" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="W35" s="190"/>
       <x:c r="X35" s="190"/>
@@ -8527,7 +8439,7 @@
       <x:c r="AH35" s="184"/>
       <x:c r="AI35" s="185"/>
       <x:c r="AJ35" s="177" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AK35" s="178"/>
       <x:c r="AL35" s="178"/>
@@ -8538,7 +8450,7 @@
       <x:c r="AQ35" s="19"/>
       <x:c r="AR35" s="19"/>
       <x:c r="AS35" s="289" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="AT35" s="290"/>
       <x:c r="AU35" s="290"/>
@@ -8563,7 +8475,7 @@
       <x:c r="BN35" s="6"/>
       <x:c r="BO35" s="7"/>
       <x:c r="BP35" s="274" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="BQ35" s="274">
         <x:v>7</x:v>
@@ -9333,7 +9245,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc86d9458a45f45b5"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57572f80fc784592"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d5d2fea07594fed"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7db58d522af4a7a"/>
 </x:worksheet>
 </file>